--- a/stories/arbres/ATOM-JEU.REG.002-02.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom joue dans la cour. Maman est là. Il y a un ballon. Maman dit une règle. La règle : on attend. Puis on passe. Tom écoute. Il prend le ballon trop vite. Maman va rappeler la règle une fois. Elle dit : on attend. C'est la règle. Tom s'arrête. Il attend. Puis il passe le ballon. Le ballon glisse. Tom sourit. Maman dit : tu as suivi la règle. Tom répète : on attend. Une règle simple. Maman la rappelle. Tom la suit.</t>
+          <t>Tom joue dans la cour. Maman est là. Il y a un ballon. Maman dit une règle. La règle : on attend. Puis on passe. Tom écoute. Il prend le ballon trop vite. Maman va rappeler la règle une fois. On attend. C'est la règle. Tom s'arrête. Il attend. Puis il passe le ballon. Le ballon glisse. Tom sourit. Tu as suivi la règle. Tom répète : on attend. Une règle simple. Maman la rappelle. Tom la suit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tom joue dans la cour. Maman est là. Il y a un ballon. Maman dit une règle. La règle : on attend. Puis on passe. Tom écoute. Il prend le ballon trop vite. Maman va rappeler la règle une fois.
+narrateur|On attend. C'est la règle.
+narrateur|Tom s'arrête. Il attend. Puis il passe le ballon. Le ballon glisse. Tom sourit.
+maman|Tu as suivi la règle.
+narrateur|Tom répète : on attend. Une règle simple. Maman la rappelle. Tom la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Tom joue. Que suit-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a suivi la règle. Il a attendu. Maman a rappelé une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Tom pose le ballon. Maman lui verse de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-02.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Tom répète : on attend. Une règle simple. Maman la rappelle. Tom la suit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Tom joue. Que suit-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Tom a suivi la règle. Il a attendu. Maman a rappelé une fois.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Tom pose le ballon. Maman lui verse de l'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.REG.002-02.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La règle de Tom</t>
+          <t>Le ballon rouge de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dans la cour, Raphaël attend, puis passe le ballon rouge. Maman rappelle la règle une fois.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom joue dans la cour. Maman est là. Il y a un ballon. Maman dit une règle. La règle : on attend. Puis on passe. Tom écoute. Il prend le ballon trop vite. Maman va rappeler la règle une fois. On attend. C'est la règle. Tom s'arrête. Il attend. Puis il passe le ballon. Le ballon glisse. Tom sourit. Tu as suivi la règle. Tom répète : on attend. Une règle simple. Maman la rappelle. Tom la suit.</t>
+          <t>Le linge blanc sèche sur la corde. Une pince de bois claque un peu. Les dalles de la cour sont chaudes. Un ballon rouge attend sous le banc. Une feuille colle à une dalle. L'ombre du linge bouge un peu. Maman plie une serviette. Elle sent le soleil et le savon. Deux pinces, une bleue, une verte. Un moineau saute près du banc. Il s'envole. Le ballon reste. Une dalle est plus chaude que l'autre. Tu as vu le ballon, Raphaël ? Oui, maman. Il est rouge. En ce moment, maman pose le ballon. Le ballon est souple et un peu chaud. Une règle. On attend. Puis on passe. J'ai envie de passer. On attend. Je te la rappelle. C'est la règle. Raphaël attend, les pieds sur une dalle. Puis il passe le ballon. Le ballon glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Raphaël. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Raphaël passe encore le ballon. La pince claque, tout doux. Tu as suivi la règle dite. Bravo. Tu as fait du bon travail. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le linge bouge encore. Les dalles restent chaudes. Encore une fois, tout doux ? Oui, maman. Raphaël attend. Puis il passe le ballon. Bravo. Tu as attendu. La feuille reste collée. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le moineau n'est plus là. Tu as les pieds sur la dalle ? Oui. Elle est chaude. On attend, puis on passe. Bravo. Raphaël pose une main sur le banc. Le bois est sec et un peu rêche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Tom joue dans la cour. Maman est là. Il y a un ballon. Maman dit une règle. La règle : on attend. Puis on passe. Tom écoute. Il prend le ballon trop vite. Maman va rappeler la règle une fois.
-narrateur|On attend. C'est la règle.
-narrateur|Tom s'arrête. Il attend. Puis il passe le ballon. Le ballon glisse. Tom sourit.
+          <t>narrateur|Le linge blanc sèche sur la corde.
+narrateur|Une pince de bois claque un peu.
+narrateur|Les dalles de la cour sont chaudes.
+narrateur|Un ballon rouge attend sous le banc.
+narrateur|Une feuille colle à une dalle.
+narrateur|L'ombre du linge bouge un peu.
+narrateur|Maman plie une serviette.
+narrateur|Elle sent le soleil et le savon.
+narrateur|Deux pinces, une bleue, une verte.
+narrateur|Un moineau saute près du banc.
+narrateur|Il s'envole.
+narrateur|Le ballon reste.
+narrateur|Une dalle est plus chaude que l'autre.
+maman|Tu as vu le ballon, Raphaël ?
+enfant-m|Oui, maman. Il est rouge.
+narrateur|En ce moment, maman pose le ballon.
+narrateur|Le ballon est souple et un peu chaud.
+maman|Une règle. On attend.
+maman|Puis on passe.
+enfant-m|J'ai envie de passer.
+maman|On attend. Je te la rappelle.
+maman|C'est la règle.
+narrateur|Raphaël attend, les pieds sur une dalle.
+narrateur|Puis il passe le ballon.
+narrateur|Le ballon glisse un peu.
+enfant-m|Il glisse.
 maman|Tu as suivi la règle.
-narrateur|Tom répète : on attend. Une règle simple. Maman la rappelle. Tom la suit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Tu as attendu. Bravo, Raphaël.
+enfant-m|On attend. Puis on passe.
+maman|Oui. Une règle simple.
+maman|Je la rappelle une fois.
+narrateur|Raphaël passe encore le ballon.
+narrateur|La pince claque, tout doux.
+maman|Tu as suivi la règle dite.
+maman|Bravo. Tu as fait du bon travail.
+enfant-m|Une règle. On attend.
+maman|Oui. On la rappelle. Tu la suis.
+narrateur|Le linge bouge encore.
+narrateur|Les dalles restent chaudes.
+maman|Encore une fois, tout doux ?
+enfant-m|Oui, maman.
+narrateur|Raphaël attend.
+narrateur|Puis il passe le ballon.
+maman|Bravo. Tu as attendu.
+narrateur|La feuille reste collée.
+enfant-m|J'ai suivi la règle.
+maman|Oui. Une règle. On la rappelle.
+narrateur|Le moineau n'est plus là.
+maman|Tu as les pieds sur la dalle ?
+enfant-m|Oui. Elle est chaude.
+maman|On attend, puis on passe. Bravo.
+narrateur|Raphaël pose une main sur le banc.
+narrateur|Le bois est sec et un peu rêche.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1403,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tom joue. Que suit-il ?</t>
+          <t>Raphaël joue. Que suit-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,10 +1559,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Tom joue. Que suit-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël joue.
+narrateur|Que suit-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom a suivi la règle. Il a attendu. Maman a rappelé une fois.</t>
+          <t>Raphaël a suivi la règle. Il a attendu. Je t'ai rappelé une fois. Une règle. On attend. Oui. Bravo, Raphaël. Le ballon repose sous le banc.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,10 +1731,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tom a suivi la règle. Il a attendu. Maman a rappelé une fois.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël a suivi la règle.
+narrateur|Il a attendu.
+maman|Je t'ai rappelé une fois.
+enfant-m|Une règle. On attend.
+maman|Oui. Bravo, Raphaël.
+narrateur|Le ballon repose sous le banc.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,7 +1763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tom pose le ballon. Maman lui verse de l'eau.</t>
+          <t>Raphaël pose le ballon. Tu veux un peu d'eau ? Oui, maman. Maman verse de l'eau. L'eau est fraîche. Merci. Le linge sent encore le savon. Le ballon reste sous le banc ? Oui. Il est rouge. La pince bleue claque encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,10 +1899,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Tom pose le ballon. Maman lui verse de l'eau.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Raphaël pose le ballon.
+maman|Tu veux un peu d'eau ?
+enfant-m|Oui, maman.
+narrateur|Maman verse de l'eau.
+narrateur|L'eau est fraîche.
+enfant-m|Merci.
+narrateur|Le linge sent encore le savon.
+maman|Le ballon reste sous le banc ?
+enfant-m|Oui. Il est rouge.
+narrateur|La pince bleue claque encore.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,7 +1935,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Raphaël. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,10 +2075,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Raphaël tient la gourde, tout près.
+enfant-m|J'ai attendu.
+maman|Oui. Tu as suivi la règle.
+maman|Bravo, Raphaël.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2138,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-02.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le linge blanc sèche sur la corde. Une pince de bois claque un peu. Les dalles de la cour sont chaudes. Un ballon rouge attend sous le banc. Une feuille colle à une dalle. L'ombre du linge bouge un peu. Maman plie une serviette. Elle sent le soleil et le savon. Deux pinces, une bleue, une verte. Un moineau saute près du banc. Il s'envole. Le ballon reste. Une dalle est plus chaude que l'autre. Tu as vu le ballon, Raphaël ? Oui, maman. Il est rouge. En ce moment, maman pose le ballon. Le ballon est souple et un peu chaud. Une règle. On attend. Puis on passe. J'ai envie de passer. On attend. Je te la rappelle. C'est la règle. Raphaël attend, les pieds sur une dalle. Puis il passe le ballon. Le ballon glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Raphaël. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Raphaël passe encore le ballon. La pince claque, tout doux. Tu as suivi la règle dite. Bravo. Tu as fait du bon travail. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le linge bouge encore. Les dalles restent chaudes. Encore une fois, tout doux ? Oui, maman. Raphaël attend. Puis il passe le ballon. Bravo. Tu as attendu. La feuille reste collée. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le moineau n'est plus là. Tu as les pieds sur la dalle ? Oui. Elle est chaude. On attend, puis on passe. Bravo. Raphaël pose une main sur le banc. Le bois est sec et un peu rêche.</t>
+          <t>Le linge blanc sèche sur la corde. Une pince de bois claque un peu. Les dalles de la cour sont chaudes. Un ballon rouge attend sous le banc. Une feuille colle à une dalle. L'ombre du linge bouge un peu. Maman plie une serviette. Elle sent le soleil et le savon. Deux pinces, une bleue, une verte. Un moineau saute près du banc. Il s'envole. Le ballon reste. Une dalle est plus chaude que l'autre. Tu as vu le ballon, Raphaël ? Oui, maman. Il est rouge. En ce moment, maman pose le ballon. Le ballon est souple et un peu chaud. Une règle. On attend. Puis on passe. J'ai envie de passer. On attend. Je te la rappelle. C'est la règle. Raphaël attend, les pieds sur une dalle. Puis il passe le ballon. Le ballon glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Raphaël. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Raphaël passe encore le ballon. La pince claque, tout doux. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le linge bouge encore. Les dalles restent chaudes. Encore une fois, tout doux ? Oui, maman. Raphaël attend. Puis il passe le ballon. Bravo. Tu as attendu. La feuille reste collée. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le moineau n'est plus là. Tu as les pieds sur la dalle ? Oui. Elle est chaude. On attend, puis on passe. Bravo. Raphaël pose une main sur le banc. Le bois est sec et un peu rêche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Tom joue dans la cour. Maman est là. Il y a un ballon. Maman dit &lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt; règle. La règle : on attend. Puis on passe. Tom écoute. Il prend le ballon trop vite. Maman va rappeler la règle une fois. Elle dit : on attend. C'est la règle. Tom s'arrête. Il attend. Puis il passe le ballon. Le ballon glisse. Tom sourit. Maman dit : tu as suivi la règle. Tom répète : on attend. Une règle simple. Maman la rappelle. Tom la suit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le linge blanc sèche sur la corde. Une pince de bois claque un peu. Les dalles de la cour sont chaudes. Un ballon rouge attend sous le banc. Une feuille colle à une dalle. L'ombre du linge bouge un peu. Maman plie une serviette. Elle sent le soleil et le savon. Deux pinces, une bleue, une verte. Un moineau saute près du banc. Il s'envole. Le ballon reste. Une dalle est plus chaude que l'autre. Tu as vu le ballon, Raphaël ? Oui, maman. Il est rouge. En ce moment, maman pose le ballon. Le ballon est souple et un peu chaud. Une règle. On attend. Puis on passe. J'ai envie de passer. On attend. Je te la rappelle. C'est la règle. Raphaël attend, les pieds sur une dalle. Puis il passe le ballon. Le ballon glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Raphaël. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Raphaël passe encore le ballon. La pince claque, tout doux. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le linge bouge encore. Les dalles restent chaudes. Encore une fois, tout doux ? Oui, maman. Raphaël attend. Puis il passe le ballon. Bravo. Tu as attendu. La feuille reste collée. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le moineau n'est plus là. Tu as les pieds sur la dalle ? Oui. Elle est chaude. On attend, puis on passe. Bravo. Raphaël pose une main sur le banc. Le bois est sec et un peu rêche.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1358,7 +1358,6 @@
 narrateur|Raphaël passe encore le ballon.
 narrateur|La pince claque, tout doux.
 maman|Tu as suivi la règle dite.
-maman|Bravo. Tu as fait du bon travail.
 enfant-m|Une règle. On attend.
 maman|Oui. On la rappelle. Tu la suis.
 narrateur|Le linge bouge encore.
@@ -1408,7 +1407,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Tom joue. Que suit-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël joue. Que suit-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1592,7 +1591,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Tom a suivi la règle. Il a attendu. Maman a rappelé &lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt; fois.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a suivi la règle. Il a attendu. Je t'ai rappelé une fois. Une règle. On attend. Oui. Bravo, Raphaël. Le ballon repose sous le banc.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1768,7 +1767,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Tom pose le ballon. Maman lui verse de l'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël pose le ballon. Tu veux un peu d'eau ? Oui, maman. Maman verse de l'eau. L'eau est fraîche. Merci. Le linge sent encore le savon. Le ballon reste sous le banc ? Oui. Il est rouge. La pince bleue claque encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,12 +1934,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Raphaël tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Raphaël. L'histoire est finie.</t>
+          <t>Raphaël tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2078,8 +2077,7 @@
           <t>narrateur|Raphaël tient la gourde, tout près.
 enfant-m|J'ai attendu.
 maman|Oui. Tu as suivi la règle.
-maman|Bravo, Raphaël.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Raphaël.</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2145,6 +2143,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-02.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cour</t>
+          <t>cour, linge sur la corde, dalles chaudes</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tom, maman</t>
+          <t>Raphaël, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-02.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-02.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le ballon rouge de Raphaël</t>
+          <t>Le ballon sous les vélos</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cour, linge sur la corde, dalles chaudes</t>
+          <t>cour d'immeuble, draps, dalles, après-midi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Raphaël, maman</t>
+          <t>Amir, maman</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dans la cour, Raphaël attend, puis passe le ballon rouge. Maman rappelle la règle une fois.</t>
+          <t>Amir veut lancer le ballon bleu à maman dans la cour. Il lance trop vite, le ballon part sous les vélos. Ils attendent un peu. Le ballon claque sur les dalles. Les draps claquent encore.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le linge blanc sèche sur la corde. Une pince de bois claque un peu. Les dalles de la cour sont chaudes. Un ballon rouge attend sous le banc. Une feuille colle à une dalle. L'ombre du linge bouge un peu. Maman plie une serviette. Elle sent le soleil et le savon. Deux pinces, une bleue, une verte. Un moineau saute près du banc. Il s'envole. Le ballon reste. Une dalle est plus chaude que l'autre. Tu as vu le ballon, Raphaël ? Oui, maman. Il est rouge. En ce moment, maman pose le ballon. Le ballon est souple et un peu chaud. Une règle. On attend. Puis on passe. J'ai envie de passer. On attend. Je te la rappelle. C'est la règle. Raphaël attend, les pieds sur une dalle. Puis il passe le ballon. Le ballon glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Raphaël. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Raphaël passe encore le ballon. La pince claque, tout doux. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le linge bouge encore. Les dalles restent chaudes. Encore une fois, tout doux ? Oui, maman. Raphaël attend. Puis il passe le ballon. Bravo. Tu as attendu. La feuille reste collée. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le moineau n'est plus là. Tu as les pieds sur la dalle ? Oui. Elle est chaude. On attend, puis on passe. Bravo. Raphaël pose une main sur le banc. Le bois est sec et un peu rêche.</t>
+          <t>Les draps blancs claquent au-dessus de la cour. Ça sent le savon chaud. Les dalles sont tièdes sous le soleil. Un pigeon gratte près du caniveau. Les vélos sont alignés contre le mur. Le caoutchouc des pneus sent un peu. Un store orange descend à une fenêtre. Amir, tu vois le ballon ? Oui, maman. Il est bleu. Le ballon attend près du banc. Il a une tache de poussière. En ce moment, Amir court vers lui. Je veux le lancer. Vers toi. J'ouvre les mains. Toi tu lances. Maman pose encore le panier. Ses mains ne sont pas prêtes. Amir prend déjà le ballon. Il le lance trop vite. Le ballon tape une dalle. Il part sous les vélos. Le pigeon s'envole. Oh. Il est parti. Il a roulé. On attend un peu ? Amir s'arrête. Les draps claquent encore. Un vélo penche un peu. Le ballon est dans l'ombre. Je le prends. Doucement. Les pédales piquent. Ils se baissent près des roues. Le métal est froid. Amir touche le ballon. Il est un peu rêche, un peu chaud. Je l'ai. On revient au milieu. Maman pose le panier contre le mur. Elle ouvre les deux mains. Tu attends que je sois prête ? Oui. On attend un peu. Amir tient le ballon contre le ventre. Il sent le caoutchouc. La cour est tout calme. Le pigeon revient, tout bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le linge blanc sèche sur la corde. Une pince de bois claque un peu. Les dalles de la cour sont chaudes. Un ballon rouge attend sous le banc. Une feuille colle à une dalle. L'ombre du linge bouge un peu. Maman plie une serviette. Elle sent le soleil et le savon. Deux pinces, une bleue, une verte. Un moineau saute près du banc. Il s'envole. Le ballon reste. Une dalle est plus chaude que l'autre. Tu as vu le ballon, Raphaël ? Oui, maman. Il est rouge. En ce moment, maman pose le ballon. Le ballon est souple et un peu chaud. Une règle. On attend. Puis on passe. J'ai envie de passer. On attend. Je te la rappelle. C'est la règle. Raphaël attend, les pieds sur une dalle. Puis il passe le ballon. Le ballon glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Raphaël. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Raphaël passe encore le ballon. La pince claque, tout doux. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le linge bouge encore. Les dalles restent chaudes. Encore une fois, tout doux ? Oui, maman. Raphaël attend. Puis il passe le ballon. Bravo. Tu as attendu. La feuille reste collée. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le moineau n'est plus là. Tu as les pieds sur la dalle ? Oui. Elle est chaude. On attend, puis on passe. Bravo. Raphaël pose une main sur le banc. Le bois est sec et un peu rêche.</t>
+          <t>Les draps blancs claquent au-dessus de la cour. Ça sent le savon chaud. Les dalles sont tièdes sous le soleil. Un pigeon gratte près du caniveau. Les vélos sont alignés contre le mur. Le caoutchouc des pneus sent un peu. Un store orange descend à une fenêtre. Amir, tu vois le ballon ? Oui, maman. Il est bleu. Le ballon attend près du banc. Il a une tache de poussière. En ce moment, Amir court vers lui. Je veux le lancer. Vers toi. J'ouvre les mains. Toi tu lances. Maman pose encore le panier. Ses mains ne sont pas prêtes. Amir prend déjà le ballon. Il le lance trop vite. Le ballon tape une dalle. Il part sous les vélos. Le pigeon s'envole. Oh. Il est parti. Il a roulé. On attend un peu ? Amir s'arrête. Les draps claquent encore. Un vélo penche un peu. Le ballon est dans l'ombre. Je le prends. Doucement. Les pédales piquent. Ils se baissent près des roues. Le métal est froid. Amir touche le ballon. Il est un peu rêche, un peu chaud. Je l'ai. On revient au milieu. Maman pose le panier contre le mur. Elle ouvre les deux mains. Tu attends que je sois prête ? Oui. On attend un peu. Amir tient le ballon contre le ventre. Il sent le caoutchouc. La cour est tout calme. Le pigeon revient, tout bas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1245,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,58 +1324,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le linge blanc sèche sur la corde.
-narrateur|Une pince de bois claque un peu.
-narrateur|Les dalles de la cour sont chaudes.
-narrateur|Un ballon rouge attend sous le banc.
-narrateur|Une feuille colle à une dalle.
-narrateur|L'ombre du linge bouge un peu.
-narrateur|Maman plie une serviette.
-narrateur|Elle sent le soleil et le savon.
-narrateur|Deux pinces, une bleue, une verte.
-narrateur|Un moineau saute près du banc.
-narrateur|Il s'envole.
-narrateur|Le ballon reste.
-narrateur|Une dalle est plus chaude que l'autre.
-maman|Tu as vu le ballon, Raphaël ?
-enfant-m|Oui, maman. Il est rouge.
-narrateur|En ce moment, maman pose le ballon.
-narrateur|Le ballon est souple et un peu chaud.
-maman|Une règle. On attend.
-maman|Puis on passe.
-enfant-m|J'ai envie de passer.
-maman|On attend. Je te la rappelle.
-maman|C'est la règle.
-narrateur|Raphaël attend, les pieds sur une dalle.
-narrateur|Puis il passe le ballon.
-narrateur|Le ballon glisse un peu.
-enfant-m|Il glisse.
-maman|Tu as suivi la règle.
-maman|Tu as attendu. Bravo, Raphaël.
-enfant-m|On attend. Puis on passe.
-maman|Oui. Une règle simple.
-maman|Je la rappelle une fois.
-narrateur|Raphaël passe encore le ballon.
-narrateur|La pince claque, tout doux.
-maman|Tu as suivi la règle dite.
-enfant-m|Une règle. On attend.
-maman|Oui. On la rappelle. Tu la suis.
-narrateur|Le linge bouge encore.
-narrateur|Les dalles restent chaudes.
-maman|Encore une fois, tout doux ?
+          <t>narrateur|Les draps blancs claquent au-dessus de la cour.
+narrateur|Ça sent le savon chaud.
+narrateur|Les dalles sont tièdes sous le soleil.
+narrateur|Un pigeon gratte près du caniveau.
+narrateur|Les vélos sont alignés contre le mur.
+narrateur|Le caoutchouc des pneus sent un peu.
+narrateur|Un store orange descend à une fenêtre.
+maman|Amir, tu vois le ballon ?
 enfant-m|Oui, maman.
-narrateur|Raphaël attend.
-narrateur|Puis il passe le ballon.
-maman|Bravo. Tu as attendu.
-narrateur|La feuille reste collée.
-enfant-m|J'ai suivi la règle.
-maman|Oui. Une règle. On la rappelle.
-narrateur|Le moineau n'est plus là.
-maman|Tu as les pieds sur la dalle ?
-enfant-m|Oui. Elle est chaude.
-maman|On attend, puis on passe. Bravo.
-narrateur|Raphaël pose une main sur le banc.
-narrateur|Le bois est sec et un peu rêche.</t>
+enfant-m|Il est bleu.
+narrateur|Le ballon attend près du banc.
+narrateur|Il a une tache de poussière.
+narrateur|En ce moment, Amir court vers lui.
+enfant-m|Je veux le lancer.
+enfant-m|Vers toi.
+maman|J'ouvre les mains.
+maman|Toi tu lances.
+narrateur|Maman pose encore le panier.
+narrateur|Ses mains ne sont pas prêtes.
+narrateur|Amir prend déjà le ballon.
+narrateur|Il le lance trop vite.
+narrateur|Le ballon tape une dalle.
+narrateur|Il part sous les vélos.
+narrateur|Le pigeon s'envole.
+enfant-m|Oh.
+enfant-m|Il est parti.
+maman|Il a roulé.
+maman|On attend un peu ?
+narrateur|Amir s'arrête.
+narrateur|Les draps claquent encore.
+narrateur|Un vélo penche un peu.
+narrateur|Le ballon est dans l'ombre.
+enfant-m|Je le prends.
+maman|Doucement.
+maman|Les pédales piquent.
+narrateur|Ils se baissent près des roues.
+narrateur|Le métal est froid.
+narrateur|Amir touche le ballon.
+narrateur|Il est un peu rêche, un peu chaud.
+enfant-m|Je l'ai.
+maman|On revient au milieu.
+narrateur|Maman pose le panier contre le mur.
+narrateur|Elle ouvre les deux mains.
+maman|Tu attends que je sois prête ?
+enfant-m|Oui.
+maman|On attend un peu.
+narrateur|Amir tient le ballon contre le ventre.
+narrateur|Il sent le caoutchouc.
+narrateur|La cour est tout calme.
+narrateur|Le pigeon revient, tout bas.</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1400,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Raphaël joue. Que suit-il ?</t>
+          <t>Amir veut lancer. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Raphaël joue. Que suit-il ?</t>
+          <t>Amir veut lancer. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1417,12 +1415,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>la règle</t>
+          <t>attendre</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la règle | une règle | attendre | on attend</t>
+          <t>attendre | on attend | un peu | son tour | elle attend | il attend | attendre un peu | on attend un peu | à son tour</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1437,7 +1435,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Maman la dit encore. C'est quoi ?</t>
+          <t>Il reste un peu. Que fait Amir d'abord ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1486,7 +1484,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1558,8 +1556,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël joue.
-narrateur|Que suit-il ?</t>
+          <t>narrateur|Amir veut lancer.
+narrateur|Que fait-il d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a suivi la règle. Il a attendu. Je t'ai rappelé une fois. Une règle. On attend. Oui. Bravo, Raphaël. Le ballon repose sous le banc.</t>
+          <t>Amir reste encore un peu. Mes mains sont ouvertes. Tu peux lancer. J'y vais. Il lance tout doux. Le ballon tape une dalle. Clac. Il arrive dans les mains de maman. Tu l'as ! Oui. Il n'est pas parti. Maman le renvoie. Amir tend les bras. Le ballon est un peu lourd. Encore une fois ? Encore. On attend un peu. Amir pose le ballon contre lui. Il regarde les mains de maman. Maintenant. Clac, encore. Les draps bougent au-dessus. Merci, Amir. Il est bleu, tout rond.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a suivi la règle. Il a attendu. Je t'ai rappelé une fois. Une règle. On attend. Oui. Bravo, Raphaël. Le ballon repose sous le banc.</t>
+          <t>Amir reste encore un peu. Mes mains sont ouvertes. Tu peux lancer. J'y vais. Il lance tout doux. Le ballon tape une dalle. Clac. Il arrive dans les mains de maman. Tu l'as ! Oui. Il n'est pas parti. Maman le renvoie. Amir tend les bras. Le ballon est un peu lourd. Encore une fois ? Encore. On attend un peu. Amir pose le ballon contre lui. Il regarde les mains de maman. Maintenant. Clac, encore. Les draps bougent au-dessus. Merci, Amir. Il est bleu, tout rond.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1647,14 +1645,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1730,12 +1728,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a suivi la règle.
-narrateur|Il a attendu.
-maman|Je t'ai rappelé une fois.
-enfant-m|Une règle. On attend.
-maman|Oui. Bravo, Raphaël.
-narrateur|Le ballon repose sous le banc.</t>
+          <t>narrateur|Amir reste encore un peu.
+maman|Mes mains sont ouvertes.
+maman|Tu peux lancer.
+enfant-m|J'y vais.
+narrateur|Il lance tout doux.
+narrateur|Le ballon tape une dalle.
+narrateur|Clac.
+narrateur|Il arrive dans les mains de maman.
+enfant-m|Tu l'as !
+maman|Oui.
+maman|Il n'est pas parti.
+narrateur|Maman le renvoie.
+narrateur|Amir tend les bras.
+narrateur|Le ballon est un peu lourd.
+maman|Encore une fois ?
+enfant-m|Encore.
+maman|On attend un peu.
+narrateur|Amir pose le ballon contre lui.
+narrateur|Il regarde les mains de maman.
+maman|Maintenant.
+narrateur|Clac, encore.
+narrateur|Les draps bougent au-dessus.
+maman|Merci, Amir.
+enfant-m|Il est bleu, tout rond.</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1778,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël pose le ballon. Tu veux un peu d'eau ? Oui, maman. Maman verse de l'eau. L'eau est fraîche. Merci. Le linge sent encore le savon. Le ballon reste sous le banc ? Oui. Il est rouge. La pince bleue claque encore.</t>
+          <t>On va boire ? J'ai soif. La gourde est dans le panier. Maman verse de l'eau. Amir boit. Une goutte tombe sur une dalle. Elle sèche tout de suite. Elle est tiède. Le ballon attend encore. Je relance ? Oui. Quand j'ai les mains. Ils reviennent au milieu. Le pigeon picore près du caniveau. Amir attend, le ballon au ventre. Tu es prêt ? Oui, maman. Il lance. Le ballon revient. Les draps claquent, plus loin. Le pigeon reste. Oui. Il n'a pas peur.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël pose le ballon. Tu veux un peu d'eau ? Oui, maman. Maman verse de l'eau. L'eau est fraîche. Merci. Le linge sent encore le savon. Le ballon reste sous le banc ? Oui. Il est rouge. La pince bleue claque encore.</t>
+          <t>On va boire ? J'ai soif. La gourde est dans le panier. Maman verse de l'eau. Amir boit. Une goutte tombe sur une dalle. Elle sèche tout de suite. Elle est tiède. Le ballon attend encore. Je relance ? Oui. Quand j'ai les mains. Ils reviennent au milieu. Le pigeon picore près du caniveau. Amir attend, le ballon au ventre. Tu es prêt ? Oui, maman. Il lance. Le ballon revient. Les draps claquent, plus loin. Le pigeon reste. Oui. Il n'a pas peur.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1823,14 +1839,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1898,16 +1914,29 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël pose le ballon.
-maman|Tu veux un peu d'eau ?
+          <t>maman|On va boire ?
+enfant-m|J'ai soif.
+narrateur|La gourde est dans le panier.
+narrateur|Maman verse de l'eau.
+narrateur|Amir boit.
+narrateur|Une goutte tombe sur une dalle.
+narrateur|Elle sèche tout de suite.
+enfant-m|Elle est tiède.
+maman|Le ballon attend encore.
+enfant-m|Je relance ?
+maman|Oui.
+maman|Quand j'ai les mains.
+narrateur|Ils reviennent au milieu.
+narrateur|Le pigeon picore près du caniveau.
+narrateur|Amir attend, le ballon au ventre.
+maman|Tu es prêt ?
 enfant-m|Oui, maman.
-narrateur|Maman verse de l'eau.
-narrateur|L'eau est fraîche.
-enfant-m|Merci.
-narrateur|Le linge sent encore le savon.
-maman|Le ballon reste sous le banc ?
-enfant-m|Oui. Il est rouge.
-narrateur|La pince bleue claque encore.</t>
+narrateur|Il lance.
+narrateur|Le ballon revient.
+narrateur|Les draps claquent, plus loin.
+enfant-m|Le pigeon reste.
+maman|Oui.
+maman|Il n'a pas peur.</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Raphaël tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Raphaël.</t>
+          <t>Le ballon est chaud. Et toi, tu as lancé. Bravo, Amir. Les draps blancs claquent encore. Le ballon bleu tient dans ses mains.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Raphaël tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Raphaël.</t>
+          <t>Le ballon est chaud. Et toi, tu as lancé. Bravo, Amir. Les draps blancs claquent encore. Le ballon bleu tient dans ses mains.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1995,14 +2024,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2074,10 +2103,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël tient la gourde, tout près.
-enfant-m|J'ai attendu.
-maman|Oui. Tu as suivi la règle.
-maman|Bravo, Raphaël.</t>
+          <t>enfant-m|Le ballon est chaud.
+maman|Et toi, tu as lancé.
+maman|Bravo, Amir.
+narrateur|Les draps blancs claquent encore.
+narrateur|Le ballon bleu tient dans ses mains.</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2148,6 +2178,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
